--- a/examples/divergent-template.xlsx
+++ b/examples/divergent-template.xlsx
@@ -10,18 +10,20 @@
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="OrganizationalUnits" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Employees" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Compensation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budgets" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Objectives" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="KeyResults" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CompanyAllocations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Compensation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Budgets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Objectives" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="KeyResults" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OrganizationalUnits'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Employees'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Compensation'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Budgets'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Objectives'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'KeyResults'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OrganizationalUnits'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Employees'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CompanyAllocations'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Compensation'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Budgets'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Objectives'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'KeyResults'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="125" customWidth="1" min="1" max="1"/>
@@ -459,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Only the example CEO name is provided by the brief; all other people, pay, relationships, and objectives are invented.</t>
+          <t>Synthetic examples use invented people and data except the named example CEO. Actual exports retain the imported records.</t>
         </is>
       </c>
     </row>
@@ -487,54 +489,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EffectiveTo and EndDate are inclusive. Compensation periods cannot overlap.</t>
+          <t>CompanyAllocations: EmployeeID and DivergentPercent (0, 25, 50, 75, 100). Set individual contributors only. Czinger gets the remainder.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Import defaults to incremental updates; omitted rows remain. Full snapshot explicitly deactivates missing employees.</t>
+          <t>Manager splits are calculated using FTE-weighted downstream contributors; they describe team composition only, not manager payroll.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>App-owned planning records are preserved. Resolve conflicts in the planning editor.</t>
+          <t>EffectiveTo and EndDate are inclusive. Compensation periods cannot overlap.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EmploymentStatus: active / leave / inactive. UnitType: company / group / department / subdepartment.</t>
+          <t>Import defaults to incremental updates; omitted rows remain. Full snapshot explicitly deactivates missing employees.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Objective Status: on-track / at-risk / off-track / complete / not-started. Direction: increase / decrease.</t>
+          <t>App-owned planning records are preserved. Resolve conflicts in the planning editor.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ApprovedEnvelope covers a unit and all descendants. DirectAllocation reserves budget for directly assigned people.</t>
+          <t>EmploymentStatus: active / leave / inactive. UnitType: company / function / group / department / team / subteam / subdepartment.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>No objective score is calculated by averaging unrelated key results.</t>
+          <t>Objective Status: on-track / at-risk / off-track / complete / not-started. Direction: increase / decrease.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>ApprovedEnvelope covers a unit and all descendants. DirectAllocation reserves budget for directly assigned people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Optional Tier: 0 company, 1 function, 2 group, 3 department, 4 team, 5+ subteam. DepartmentCode is text; duplicates are allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>No objective score is calculated by averaging unrelated key results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>All IDs, references, dates, FTE, pay, owners, hierarchies, and intervals are validated before commit.</t>
         </is>
@@ -551,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -559,6 +582,8 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -587,9 +612,19 @@
           <t>OwnerEmployeeID</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>DepartmentCode</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -600,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -614,6 +649,8 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -672,14 +709,55 @@
           <t>EmploymentType</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>SourceCompany</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>FTEBasis</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EmployeeID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DivergentPercent</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -740,7 +818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -795,7 +873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -862,7 +940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/examples/divergent-template.xlsx
+++ b/examples/divergent-template.xlsx
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OrganizationalUnits'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Employees'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Employees'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CompanyAllocations'!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Compensation'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Compensation'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Budgets'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Objectives'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'KeyResults'!$A$1:$J$1</definedName>
@@ -475,7 +475,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pay fields are actual annual amounts at contracted FTE. Do not multiply by FTE again. Blank pay means unknown.</t>
+          <t>PayBasis: salary (annual base + annual bonus), hourly (HourlyRate x AnnualHours), monthly (MonthlyRate x 12). Blank PayBasis retains legacy annual amounts. Never multiply pay by FTE again.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EmploymentStatus: active / leave / inactive. UnitType: company / function / group / department / team / subteam / subdepartment.</t>
+          <t>EmploymentType: FTE or Contractor; FTE ExemptionStatus: exempt or non-exempt. EmploymentStatus: active / leave / inactive / vacant / draft. UnitType: company / function / group / department / team / subteam / subdepartment.</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -651,6 +651,7 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,17 +712,22 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>ExemptionStatus</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>SourceCompany</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>FTEBasis</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -763,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -773,6 +779,10 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -811,9 +821,29 @@
           <t>AnnualEmployerCosts</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PayBasis</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>HourlyRate</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>AnnualHours</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MonthlyRate</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/examples/divergent-template.xlsx
+++ b/examples/divergent-template.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Employees'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CompanyAllocations'!$A$1:$B$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Compensation'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Budgets'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Budgets'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Objectives'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'KeyResults'!$A$1:$J$1</definedName>
   </definedNames>
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IDs are text. Preserve leading zeros. Dates use YYYY-MM-DD. Currency defaults to USD; annual budgets use calendar years.</t>
+          <t>IDs are text. Preserve leading zeros. Dates use YYYY-MM-DD. Currency defaults to USD; annual budgets use calendar years. Company budgets use ApprovedEnvelope dollars; child budgets use AllocationPercent of their parent. DirectPercent reserves a share for directly assigned employees.</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -863,6 +863,8 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,9 +898,19 @@
           <t>DirectAllocation</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>AllocationPercent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DirectPercent</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
